--- a/naver-place-crawler/results_health/김포_PT.xlsx
+++ b/naver-place-crawler/results_health/김포_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>위너핏 마송점</t>
+          <t>라임 피트니스 PT 김포장기점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>boos66@naver.com</t>
+          <t>lime___fitness@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1319-4816</t>
+          <t>0507-1381-7494</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 김포시 통진읍 마송1로84번길 53 7층</t>
+          <t>경기 김포시 태장로 780 베네치아의 아침 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/boos66</t>
+          <t>https://blog.naver.com/lime___fitness</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,10 +606,14 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hh9p</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>114</v>
+        <v>480</v>
       </c>
       <c r="Q2" t="n">
-        <v>167</v>
+        <v>492</v>
       </c>
       <c r="R2" t="n">
-        <v>281</v>
+        <v>972</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,51 +640,51 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1043243355</t>
+          <t>1802881557</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043243355</t>
+          <t>https://m.place.naver.com/place/1802881557</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>매스짐 헬스&amp;PT 풍무점</t>
+          <t>포워드 휘트니스 감정점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>fmgym123@naver.com</t>
+          <t>forward-fitness2@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1321-7391</t>
+          <t>0507-1414-6704</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 김포시 유현로238번길 11 드림프라자 8층 매스짐</t>
+          <t>경기 김포시 중봉1로 17 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/fmgym123</t>
+          <t>https://www.instagram.com/forward.fitness.02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,15 +699,19 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w936str</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -715,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>136</v>
+        <v>338</v>
       </c>
       <c r="Q3" t="n">
-        <v>529</v>
+        <v>585</v>
       </c>
       <c r="R3" t="n">
-        <v>665</v>
+        <v>923</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,51 +738,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1933746777</t>
+          <t>1451785502</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1933746777</t>
+          <t>https://m.place.naver.com/place/1451785502</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>김포 장기동 스웻바이브 그룹PT 하이록스 제휴센터</t>
+          <t>위너핏 마송점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>edew1@naver.com</t>
+          <t>boos66@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1336-1197</t>
+          <t>0507-1319-4816</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 김포시 청송로 8 석권프라자 5층 스웻바이브</t>
+          <t>경기 김포시 통진읍 마송1로84번길 53 7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sweat_vibe</t>
+          <t>https://blog.naver.com/boos66</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -789,15 +797,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5w0ua</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>435</v>
+        <v>115</v>
       </c>
       <c r="Q4" t="n">
-        <v>468</v>
+        <v>175</v>
       </c>
       <c r="R4" t="n">
-        <v>903</v>
+        <v>290</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,51 +836,51 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1827206561</t>
+          <t>1043243355</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1827206561</t>
+          <t>https://m.place.naver.com/place/1043243355</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G1 헬스&amp;PT 고촌점</t>
+          <t>원알엠 PT&amp;헬스 풍무점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dmak77@naver.com</t>
+          <t>sheep_coach@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1358-1783</t>
+          <t>0507-1417-8271</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 김포시 고촌읍 수기로 115 센트럴타워 505호~507호</t>
+          <t>경기 김포시 풍무로 105 가동 제6층 602호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dmak77?tab=1</t>
+          <t>https://blog.naver.com/sheep_coach</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -888,10 +900,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/ww7sj2s</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>298</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>258</v>
+        <v>99</v>
       </c>
       <c r="R5" t="n">
-        <v>556</v>
+        <v>129</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +934,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1747463295</t>
+          <t>2035326726</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747463295</t>
+          <t>https://m.place.naver.com/place/2035326726</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -940,34 +956,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>인어스휘트니스 헬스 PT &amp; 필라테스 골프 김포점</t>
+          <t>빠짐 헬스&amp;재활PT 장기역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>inus-fitness09@naver.com</t>
+          <t>jppark4@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1312-8337</t>
+          <t>0507-1316-2928</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강4로 113 신한프라자 10층</t>
+          <t>경기 김포시 김포한강1로97번길 32-32 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://inushnl.com/layout/fitness/home.php?go=main&amp;</t>
+          <t>https://blog.naver.com/jppark4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -977,15 +993,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcefw2</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>1410</v>
+        <v>70</v>
       </c>
       <c r="Q6" t="n">
-        <v>784</v>
+        <v>409</v>
       </c>
       <c r="R6" t="n">
-        <v>2194</v>
+        <v>479</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,51 +1032,51 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1901435715</t>
+          <t>1324417059</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1901435715</t>
+          <t>https://m.place.naver.com/place/1324417059</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>원알엠 PT&amp;헬스 풍무점</t>
+          <t>G1 헬스&amp;PT 고촌점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>sheep_coach@naver.com</t>
+          <t>dmak77@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1417-8271</t>
+          <t>0507-1358-1783</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 김포시 풍무로 105 가동 제6층 602호</t>
+          <t>경기 김포시 고촌읍 수기로 115 센트럴타워 505호~507호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sheep_coach</t>
+          <t>https://blog.naver.com/dmak77?tab=1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1091,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>29</v>
+        <v>298</v>
       </c>
       <c r="Q7" t="n">
-        <v>98</v>
+        <v>256</v>
       </c>
       <c r="R7" t="n">
-        <v>127</v>
+        <v>554</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,51 +1126,51 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2035326726</t>
+          <t>1747463295</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2035326726</t>
+          <t>https://m.place.naver.com/place/1747463295</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>에이플러스짐 헬스&amp;PT 김포장기점</t>
+          <t>김포 장기동 스웻바이브 그룹PT 하이록스 제휴센터</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>aplusgym110@naver.com</t>
+          <t>edew1@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1435-3035</t>
+          <t>0507-1336-1197</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로51번길 36 2층</t>
+          <t>경기 김포시 청송로 8 석권프라자 5층 스웻바이브</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/aplusgym110/223290165820</t>
+          <t>https://www.instagram.com/sweat_vibe</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1165,18 +1185,22 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4ppewx</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1185,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="Q8" t="n">
-        <v>752</v>
+        <v>472</v>
       </c>
       <c r="R8" t="n">
-        <v>1197</v>
+        <v>907</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1224,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1652716053</t>
+          <t>1827206561</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1652716053</t>
+          <t>https://m.place.naver.com/place/1827206561</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>루온짐PT 김포 장기점</t>
+          <t>플랜휘트니스 사우역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>luongym@naver.com</t>
+          <t>planfitness89@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1355-1592</t>
+          <t>0507-1395-4251</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강2로 110 센타프라자 3층 301호</t>
+          <t>경기 김포시 사우중로 87 5층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luon.gym</t>
+          <t>https://blog.naver.com/planfitness89</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1259,15 +1283,19 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wavreq8</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1279,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>114</v>
+        <v>331</v>
       </c>
       <c r="Q9" t="n">
-        <v>429</v>
+        <v>194</v>
       </c>
       <c r="R9" t="n">
-        <v>543</v>
+        <v>525</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,51 +1322,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1024850213</t>
+          <t>1427280856</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024850213</t>
+          <t>https://m.place.naver.com/place/1427280856</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>올데이짐</t>
+          <t>헨트 피트니스 헬스&amp;PT 풍무점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>chodochi@naver.com</t>
+          <t>hentfitness@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1376-4881</t>
+          <t>0507-1310-2603</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강2로 92 메이플 플라자 1동 301호</t>
+          <t>경기 김포시 풍무로 112 4층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/chodochi</t>
+          <t>https://open.kakao.com/o/sO2iZ5Bh</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1358,13 +1386,17 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4spk6</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1373,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>277</v>
+        <v>203</v>
       </c>
       <c r="Q10" t="n">
-        <v>240</v>
+        <v>713</v>
       </c>
       <c r="R10" t="n">
-        <v>517</v>
+        <v>916</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1388,51 +1420,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1862726547</t>
+          <t>1735469913</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1862726547</t>
+          <t>https://m.place.naver.com/place/1735469913</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>뉴라이프짐그룹PT장기본점</t>
+          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>conaya17@naver.com</t>
+          <t>lounge_fitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1421-4776</t>
+          <t>0507-1360-7495</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 김포시 초당로61번길 51 뉴라이프짐</t>
+          <t>경기 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/conaya17</t>
+          <t>https://blog.naver.com/lounge_fitness</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1452,10 +1484,14 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w42s1j</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>X</t>
@@ -1467,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43</v>
+        <v>304</v>
       </c>
       <c r="Q11" t="n">
-        <v>156</v>
+        <v>268</v>
       </c>
       <c r="R11" t="n">
-        <v>199</v>
+        <v>572</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1482,17 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1060451309</t>
+          <t>1798562504</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1060451309</t>
+          <t>https://m.place.naver.com/place/1798562504</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
@@ -1504,29 +1540,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>웰리브라운지 PT 필라테스 구래동점</t>
+          <t>모멘핏 재활PT 장기점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>withusfitness@naver.com</t>
+          <t>dailyfitmemo@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1368-7369</t>
+          <t>0507-1338-0549</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강8로 386 1001-1004호</t>
+          <t>경기 김포시 김포한강3로237번길 10 1동 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/welliv.lounge</t>
+          <t>https://www.instagram.com/momentfit_janggi</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1546,10 +1582,14 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wgsn8pz</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
           <t>X</t>
@@ -1561,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>489</v>
+        <v>14</v>
       </c>
       <c r="Q12" t="n">
-        <v>621</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
-        <v>1110</v>
+        <v>34</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1576,56 +1616,56 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1523485481</t>
+          <t>2096364009</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1523485481</t>
+          <t>https://m.place.naver.com/place/2096364009</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스포츠,오락</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>빠짐 헬스&amp;재활PT 장기역점</t>
+          <t>오픈도어복싱센터 ODBC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>jppark4@naver.com</t>
+          <t>odbc221008@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1316-2928</t>
+          <t>0507-1391-0736</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로97번길 32-32 1층</t>
+          <t>경기 김포시 김포한강8로148번길 8-10 1층 102호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jppark4</t>
+          <t>https://opendoorboxing.imweb.me/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1640,13 +1680,17 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5i4rg</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1655,13 +1699,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="Q13" t="n">
-        <v>339</v>
+        <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>409</v>
+        <v>200</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1670,773 +1714,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1324417059</t>
+          <t>1391709606</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324417059</t>
+          <t>https://m.place.naver.com/place/1391709606</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>짐원휘트니스 구래2호점 헬스PT</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>gymonelab@naver.com</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0507-1438-9680</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>경기도 김포시 김포한강8로 400 홍은프라자 4층</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>http://gymone.kr</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P14" t="n">
-        <v>1023</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>347</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1370</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>1143886551</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1143886551</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>엑스짐 헬스 PT 김포장기동점</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>cltnzz6736@naver.com</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0507-1327-6736</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>경기도 김포시 김포한강4로 129 하나프라자 7층</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>https://zhenghwun91.wixsite.com/xgym</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P15" t="n">
-        <v>224</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>185</v>
-      </c>
-      <c r="R15" t="n">
-        <v>409</v>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>1567234519</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1567234519</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>여성전용PT투프로짐 김포점</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>2progym2@naver.com</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0507-1305-8913</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>경기도 김포시 김포한강4로 513 채움테라스 3층 302호, 304호</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/2progym2</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>117</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>218</v>
-      </c>
-      <c r="R16" t="n">
-        <v>335</v>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>1050488006</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1050488006</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>프로맨스짐 PT</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>promansgym1@naver.com</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0507-1378-5369</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>경기도 김포시 김포한강1로 57 5층 프로맨스짐</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://link.inpock.co.kr/promansgym</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P17" t="n">
-        <v>147</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>639</v>
-      </c>
-      <c r="R17" t="n">
-        <v>786</v>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>1770635333</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1770635333</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>스포츠시설</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>브이짐 헬스&amp;PT 풍무점</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>lki666@naver.com</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0507-1433-9679</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>경기도 김포시 풍무로 20 스타프라자</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/lki666</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P18" t="n">
-        <v>115</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>440</v>
-      </c>
-      <c r="R18" t="n">
-        <v>555</v>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>1075826288</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1075826288</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>디엠짐 헬스&amp;PT 풍무점</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>ehdals1278@naver.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0507-1332-9584</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>경기도 김포시 풍무로 128 4층 418호, 419호</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://blog.naver.com/ehdals1278</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P19" t="n">
-        <v>110</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>477</v>
-      </c>
-      <c r="R19" t="n">
-        <v>587</v>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>1294358945</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1294358945</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>더문짐 &amp; 그룹PT 장기동</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>prest4@naver.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0507-1370-2206</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>경기도 김포시 태장로 808 송호프라자 2층 203호 더문짐 &amp; 그룹PT</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/gimpo_themoongym/</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P20" t="n">
-        <v>101</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>53</v>
-      </c>
-      <c r="R20" t="n">
-        <v>154</v>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>1973053063</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1973053063</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>스포츠,오락</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>STA PT 김포구래점</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>sta_pt@naver.com</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>help@brunch.co.kr</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0507-1492-0190</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>경기도 김포시 김포한강8로 410 9층 STA PT</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>https://open.kakao.com/me/sta_pthttp://pf.kakao.com/_EnYeK/chat</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>123</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>171</v>
-      </c>
-      <c r="R21" t="n">
-        <v>294</v>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>1129851786</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1129851786</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>2026-04-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/김포_PT.xlsx
+++ b/naver-place-crawler/results_health/김포_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>라임 피트니스 PT 김포장기점</t>
+          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lime___fitness@naver.com</t>
+          <t>lounge_fitness@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1381-7494</t>
+          <t>0507-1360-7495</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기 김포시 태장로 780 베네치아의 아침 3층</t>
+          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lime___fitness</t>
+          <t>https://blog.naver.com/lounge_fitness</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4hh9p</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -625,13 +621,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>480</v>
+        <v>304</v>
       </c>
       <c r="Q2" t="n">
-        <v>492</v>
+        <v>268</v>
       </c>
       <c r="R2" t="n">
-        <v>972</v>
+        <v>572</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -640,17 +636,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1802881557</t>
+          <t>1798562504</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1802881557</t>
+          <t>https://m.place.naver.com/place/1798562504</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -726,10 +722,10 @@
         <v>338</v>
       </c>
       <c r="Q3" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="R3" t="n">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -748,41 +744,41 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>위너핏 마송점</t>
+          <t>라임 피트니스 PT 김포장기점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>boos66@naver.com</t>
+          <t>lime___fitness@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1319-4816</t>
+          <t>0507-1381-7494</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 김포시 통진읍 마송1로84번길 53 7층</t>
+          <t>경기 김포시 태장로 780 베네치아의 아침 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/boos66</t>
+          <t>https://blog.naver.com/lime___fitness</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5w0ua</t>
+          <t>https://talk.naver.com/ct/w4hh9p</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -821,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>115</v>
+        <v>480</v>
       </c>
       <c r="Q4" t="n">
-        <v>175</v>
+        <v>493</v>
       </c>
       <c r="R4" t="n">
-        <v>290</v>
+        <v>973</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -836,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1043243355</t>
+          <t>1802881557</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043243355</t>
+          <t>https://m.place.naver.com/place/1802881557</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -858,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>원알엠 PT&amp;헬스 풍무점</t>
+          <t>위너핏 마송점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>sheep_coach@naver.com</t>
+          <t>boos66@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1417-8271</t>
+          <t>0507-1319-4816</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 김포시 풍무로 105 가동 제6층 602호</t>
+          <t>경기 김포시 통진읍 마송1로84번길 53 7층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sheep_coach</t>
+          <t>https://blog.naver.com/boos66</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -905,7 +901,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/ww7sj2s</t>
+          <t>https://talk.naver.com/ct/w5w0ua</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -919,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="Q5" t="n">
-        <v>99</v>
+        <v>177</v>
       </c>
       <c r="R5" t="n">
-        <v>129</v>
+        <v>292</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -934,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2035326726</t>
+          <t>1043243355</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2035326726</t>
+          <t>https://m.place.naver.com/place/1043243355</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -956,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>빠짐 헬스&amp;재활PT 장기역점</t>
+          <t>원알엠 PT&amp;헬스 풍무점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>jppark4@naver.com</t>
+          <t>sheep_coach@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1316-2928</t>
+          <t>0507-1417-8271</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강1로97번길 32-32 1층</t>
+          <t>경기 김포시 풍무로 105 가동 제6층 602호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jppark4</t>
+          <t>https://blog.naver.com/sheep_coach</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1003,7 +999,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wcefw2</t>
+          <t>https://talk.naver.com/ct/ww7sj2s</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1017,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="Q6" t="n">
-        <v>409</v>
+        <v>99</v>
       </c>
       <c r="R6" t="n">
-        <v>479</v>
+        <v>129</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1032,17 +1028,17 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1324417059</t>
+          <t>2035326726</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324417059</t>
+          <t>https://m.place.naver.com/place/2035326726</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1054,29 +1050,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>G1 헬스&amp;PT 고촌점</t>
+          <t>빠짐 헬스&amp;재활PT 장기역점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dmak77@naver.com</t>
+          <t>jppark4@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1358-1783</t>
+          <t>0507-1316-2928</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 김포시 고촌읍 수기로 115 센트럴타워 505호~507호</t>
+          <t>경기 김포시 김포한강1로97번길 32-32 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dmak77?tab=1</t>
+          <t>https://blog.naver.com/jppark4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1096,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcefw2</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>298</v>
+        <v>70</v>
       </c>
       <c r="Q7" t="n">
-        <v>256</v>
+        <v>409</v>
       </c>
       <c r="R7" t="n">
-        <v>554</v>
+        <v>479</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1747463295</t>
+          <t>1324417059</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747463295</t>
+          <t>https://m.place.naver.com/place/1324417059</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>김포 장기동 스웻바이브 그룹PT 하이록스 제휴센터</t>
+          <t>G1 헬스&amp;PT 고촌점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>edew1@naver.com</t>
+          <t>dmak77@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1336-1197</t>
+          <t>0507-1358-1783</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 김포시 청송로 8 석권프라자 5층 스웻바이브</t>
+          <t>경기 김포��� 고촌읍 수기로 115 센트럴타워 505호~507호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sweat_vibe</t>
+          <t>https://blog.naver.com/dmak77?tab=1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,22 +1185,18 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ppewx</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1209,13 +1205,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>435</v>
+        <v>298</v>
       </c>
       <c r="Q8" t="n">
-        <v>472</v>
+        <v>256</v>
       </c>
       <c r="R8" t="n">
-        <v>907</v>
+        <v>554</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1224,51 +1220,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1827206561</t>
+          <t>1747463295</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1827206561</t>
+          <t>https://m.place.naver.com/place/1747463295</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>플랜휘트니스 사우역점</t>
+          <t>루온짐PT 김포 장기점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>planfitness89@naver.com</t>
+          <t>luongym@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1395-4251</t>
+          <t>0507-1355-1592</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 김포시 사우중로 87 5층</t>
+          <t>경기 김포시 김포한강2로 110 센타프라자 3층 301호</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/planfitness89</t>
+          <t>https://www.instagram.com/luon.gym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1283,7 +1279,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1293,7 +1289,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wavreq8</t>
+          <t>https://talk.naver.com/ct/wvx1m86</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1307,13 +1303,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>331</v>
+        <v>117</v>
       </c>
       <c r="Q9" t="n">
-        <v>194</v>
+        <v>437</v>
       </c>
       <c r="R9" t="n">
-        <v>525</v>
+        <v>554</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1322,17 +1318,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1427280856</t>
+          <t>1024850213</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1427280856</t>
+          <t>https://m.place.naver.com/place/1024850213</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
@@ -1344,29 +1340,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>헨트 피트니스 헬스&amp;PT 풍무점</t>
+          <t>플랜휘트니스 사우역점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hentfitness@naver.com</t>
+          <t>planfitness89@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1310-2603</t>
+          <t>0507-1395-4251</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 김포시 풍무로 112 4층</t>
+          <t>경기 김포시 사우중로 87 5층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sO2iZ5Bh</t>
+          <t>https://blog.naver.com/planfitness89</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1381,7 +1377,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1391,12 +1387,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4spk6</t>
+          <t>https://talk.naver.com/ct/wavreq8</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1405,13 +1401,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>203</v>
+        <v>331</v>
       </c>
       <c r="Q10" t="n">
-        <v>713</v>
+        <v>194</v>
       </c>
       <c r="R10" t="n">
-        <v>916</v>
+        <v>525</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1420,51 +1416,51 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1735469913</t>
+          <t>1427280856</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735469913</t>
+          <t>https://m.place.naver.com/place/1427280856</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
+          <t>모멘핏 재활PT 장기점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lounge_fitness@naver.com</t>
+          <t>dailyfitmemo@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1360-7495</t>
+          <t>0507-1338-0549</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
+          <t>경기 김포시 김포한강3로237번길 10 1동 2층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lounge_fitness</t>
+          <t>https://www.instagram.com/momentfit_janggi</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1479,7 +1475,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1489,7 +1485,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w42s1j</t>
+          <t>https://talk.naver.com/ct/wgsn8pz</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1503,13 +1499,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>304</v>
+        <v>14</v>
       </c>
       <c r="Q11" t="n">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="R11" t="n">
-        <v>572</v>
+        <v>34</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1518,51 +1514,51 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1798562504</t>
+          <t>2096364009</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798562504</t>
+          <t>https://m.place.naver.com/place/2096364009</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>모멘핏 재활PT 장기점</t>
+          <t>오픈도어복싱센터 ODBC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>dailyfitmemo@naver.com</t>
+          <t>odbc221008@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1338-0549</t>
+          <t>0507-1391-0736</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강3로237번길 10 1동 2층</t>
+          <t>경기 김포시 김포한강8로148번길 8-10 1층 102호</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/momentfit_janggi</t>
+          <t>https://opendoorboxing.imweb.me/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1577,7 +1573,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1587,7 +1583,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wgsn8pz</t>
+          <t>https://talk.naver.com/ct/w5i4rg</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1601,13 +1597,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="Q12" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="R12" t="n">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1616,56 +1612,52 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2096364009</t>
+          <t>1391709606</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2096364009</t>
+          <t>https://m.place.naver.com/place/1391709606</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>오픈도어복싱센터 ODBC</t>
+          <t>휘트니스바로PT 고촌점</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>odbc221008@naver.com</t>
+          <t>fitnessbaro_2@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0507-1391-0736</t>
-        </is>
-      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강8로148번길 8-10 1층 102호</t>
+          <t>경기 김포시 고촌읍 태리로 293 3층</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://opendoorboxing.imweb.me/</t>
+          <t>https://smartstore.naver.com/fitnessbaro</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1675,7 +1667,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1685,12 +1677,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5i4rg</t>
+          <t>https://talk.naver.com/ct/wajkmaq</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1699,13 +1691,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="Q13" t="n">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="R13" t="n">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1714,17 +1706,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1391709606</t>
+          <t>2065106460</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1391709606</t>
+          <t>https://m.place.naver.com/place/2065106460</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-26</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/김포_PT.xlsx
+++ b/naver-place-crawler/results_health/김포_PT.xlsx
@@ -426,7 +426,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="41" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
     <col width="46" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
@@ -564,29 +564,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
+          <t>포워드 휘트니스 감정점</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>lounge_fitness@naver.com</t>
+          <t>forward-fitness2@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1360-7495</t>
+          <t>0507-1414-6704</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
+          <t>경기 김포시 중봉1로 17 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lounge_fitness</t>
+          <t>https://www.instagram.com/forward.fitness.02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -601,15 +601,19 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w936str</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -621,13 +625,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>304</v>
+        <v>338</v>
       </c>
       <c r="Q2" t="n">
-        <v>268</v>
+        <v>586</v>
       </c>
       <c r="R2" t="n">
-        <v>572</v>
+        <v>924</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +640,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1798562504</t>
+          <t>1451785502</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1798562504</t>
+          <t>https://m.place.naver.com/place/1451785502</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -658,29 +662,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>포워드 휘트니스 감정점</t>
+          <t>라임 피트니스 PT 김포장기점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>forward-fitness2@naver.com</t>
+          <t>lime___fitness@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0507-1414-6704</t>
+          <t>0507-1381-7494</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기 김포시 중봉1로 17 4층</t>
+          <t>경기 김포시 태장로 780 베네치아의 아침 3층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/forward.fitness.02</t>
+          <t>https://blog.naver.com/lime___fitness</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -695,7 +699,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -705,7 +709,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w936str</t>
+          <t>https://talk.naver.com/ct/w4hh9p</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -719,13 +723,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>338</v>
+        <v>480</v>
       </c>
       <c r="Q3" t="n">
-        <v>586</v>
+        <v>493</v>
       </c>
       <c r="R3" t="n">
-        <v>924</v>
+        <v>973</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,12 +738,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1451785502</t>
+          <t>1802881557</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1451785502</t>
+          <t>https://m.place.naver.com/place/1802881557</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -751,34 +755,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>라임 피트니스 PT 김포장기점</t>
+          <t>위너핏 마송점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lime___fitness@naver.com</t>
+          <t>boos66@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1381-7494</t>
+          <t>0507-1319-4816</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기 김포시 태장로 780 베네치아의 아침 3층</t>
+          <t>경기 김포시 통진읍 마송1로84번길 53 7층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/lime___fitness</t>
+          <t>https://blog.naver.com/boos66</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -803,7 +807,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w4hh9p</t>
+          <t>https://talk.naver.com/ct/w5w0ua</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -817,13 +821,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>480</v>
+        <v>115</v>
       </c>
       <c r="Q4" t="n">
-        <v>493</v>
+        <v>177</v>
       </c>
       <c r="R4" t="n">
-        <v>973</v>
+        <v>292</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -832,12 +836,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1802881557</t>
+          <t>1043243355</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1802881557</t>
+          <t>https://m.place.naver.com/place/1043243355</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -854,29 +858,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>위너핏 마송점</t>
+          <t>원알엠 PT&amp;헬스 풍무점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>boos66@naver.com</t>
+          <t>sheep_coach@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1319-4816</t>
+          <t>0507-1417-8271</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기 김포시 통진읍 마송1로84번길 53 7층</t>
+          <t>경기 김포시 풍무로 105 가동 제6층 602호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/boos66</t>
+          <t>https://blog.naver.com/sheep_coach</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -901,7 +905,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5w0ua</t>
+          <t>https://talk.naver.com/ct/ww7sj2s</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -915,13 +919,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>177</v>
+        <v>99</v>
       </c>
       <c r="R5" t="n">
-        <v>292</v>
+        <v>129</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -930,12 +934,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1043243355</t>
+          <t>2035326726</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043243355</t>
+          <t>https://m.place.naver.com/place/2035326726</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -952,29 +956,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>원알엠 PT&amp;헬스 풍무점</t>
+          <t>빠짐 헬스&amp;재활PT 장기역점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>sheep_coach@naver.com</t>
+          <t>jppark4@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1417-8271</t>
+          <t>0507-1316-2928</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기 김포시 풍무로 105 가동 제6층 602호</t>
+          <t>경기 김포시 김포한강1로97번길 32-32 1층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sheep_coach</t>
+          <t>https://blog.naver.com/jppark4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -999,7 +1003,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/ww7sj2s</t>
+          <t>https://talk.naver.com/ct/wcefw2</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1013,13 +1017,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="Q6" t="n">
-        <v>99</v>
+        <v>409</v>
       </c>
       <c r="R6" t="n">
-        <v>129</v>
+        <v>479</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1028,12 +1032,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2035326726</t>
+          <t>1324417059</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2035326726</t>
+          <t>https://m.place.naver.com/place/1324417059</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1050,29 +1054,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>빠짐 헬스&amp;재활PT 장기역점</t>
+          <t>G1 헬스&amp;PT 고촌점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jppark4@naver.com</t>
+          <t>dmak77@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1316-2928</t>
+          <t>0507-1358-1783</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강1로97번길 32-32 1층</t>
+          <t>경기 김포시 고촌읍 수기로 115 센트럴타워 505호~507호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jppark4</t>
+          <t>https://blog.naver.com/dmak77?tab=1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1092,14 +1096,10 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wcefw2</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>70</v>
+        <v>298</v>
       </c>
       <c r="Q7" t="n">
-        <v>409</v>
+        <v>256</v>
       </c>
       <c r="R7" t="n">
-        <v>479</v>
+        <v>554</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1324417059</t>
+          <t>1747463295</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324417059</t>
+          <t>https://m.place.naver.com/place/1747463295</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1148,29 +1148,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G1 헬스&amp;PT 고촌점</t>
+          <t>루온짐PT 김포 장기점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dmak77@naver.com</t>
+          <t>luongym@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1358-1783</t>
+          <t>0507-1355-1592</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기 김포��� 고촌읍 수기로 115 센트럴타워 505호~507호</t>
+          <t>경기 김포시 김포한강2로 110 센타프라자 3층 301호</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dmak77?tab=1</t>
+          <t>https://www.instagram.com/luon.gym</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,15 +1185,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wvx1m86</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1205,10 +1209,10 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>298</v>
+        <v>117</v>
       </c>
       <c r="Q8" t="n">
-        <v>256</v>
+        <v>437</v>
       </c>
       <c r="R8" t="n">
         <v>554</v>
@@ -1220,12 +1224,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1747463295</t>
+          <t>1024850213</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747463295</t>
+          <t>https://m.place.naver.com/place/1024850213</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1242,44 +1246,44 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>루온짐PT 김포 장기점</t>
+          <t>엑스짐 헬스 PT 김포장기동점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>luongym@naver.com</t>
+          <t>cltnzz6736@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1355-1592</t>
+          <t>0507-1327-6736</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강2로 110 센타프라자 3층 301호</t>
+          <t>경기 김포시 김포한강4로 129 하나프라자 7층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luon.gym</t>
+          <t>https://zhenghwun91.wixsite.com/xgym</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1289,12 +1293,12 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wvx1m86</t>
+          <t>https://talk.naver.com/ct/w497xw</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1303,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>117</v>
+        <v>224</v>
       </c>
       <c r="Q9" t="n">
-        <v>437</v>
+        <v>186</v>
       </c>
       <c r="R9" t="n">
-        <v>554</v>
+        <v>410</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1318,12 +1322,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1024850213</t>
+          <t>1567234519</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024850213</t>
+          <t>https://m.place.naver.com/place/1567234519</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1433,34 +1437,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>모멘핏 재활PT 장기점</t>
+          <t>라운지 휘트니스 헬스&amp;PT&amp;GX&amp;스피닝&amp;필라 운양점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dailyfitmemo@naver.com</t>
+          <t>lounge_fitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1338-0549</t>
+          <t>0507-1360-7495</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강3로237번길 10 1동 2층</t>
+          <t>경기 김포시 김포한강1로 230 9층 901~907, 922~925호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/momentfit_janggi</t>
+          <t>https://blog.naver.com/lounge_fitness</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1475,7 +1479,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1485,7 +1489,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wgsn8pz</t>
+          <t>https://talk.naver.com/ct/w42s1j</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1499,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>14</v>
+        <v>304</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>268</v>
       </c>
       <c r="R11" t="n">
-        <v>34</v>
+        <v>572</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1514,12 +1518,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2096364009</t>
+          <t>1798562504</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2096364009</t>
+          <t>https://m.place.naver.com/place/1798562504</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1531,34 +1535,34 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>오픈도어복싱센터 ODBC</t>
+          <t>모멘핏 재활PT 장기점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>odbc221008@naver.com</t>
+          <t>dailyfitmemo@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0507-1391-0736</t>
+          <t>0507-1338-0549</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강8로148번길 8-10 1층 102호</t>
+          <t>경기 김포시 김포한강3로237번길 10 1동 2층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://opendoorboxing.imweb.me/</t>
+          <t>https://www.instagram.com/momentfit_janggi</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1573,7 +1577,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1583,7 +1587,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5i4rg</t>
+          <t>https://talk.naver.com/ct/wgsn8pz</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1597,13 +1601,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>95</v>
+        <v>14</v>
       </c>
       <c r="Q12" t="n">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="R12" t="n">
-        <v>200</v>
+        <v>34</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1612,12 +1616,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1391709606</t>
+          <t>2096364009</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1391709606</t>
+          <t>https://m.place.naver.com/place/2096364009</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1629,35 +1633,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>휘트니스바로PT 고촌점</t>
+          <t>오픈도어복싱센터 ODBC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>fitnessbaro_2@naver.com</t>
+          <t>odbc221008@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1391-0736</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>경기 김포시 고촌읍 태리로 293 3층</t>
+          <t>경기 김포시 김포한강8로148번길 8-10 1층 102호</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/fitnessbaro</t>
+          <t>https://opendoorboxing.imweb.me/</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1667,7 +1675,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1677,12 +1685,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wajkmaq</t>
+          <t>https://talk.naver.com/ct/w5i4rg</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1691,13 +1699,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="Q13" t="n">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="R13" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1706,12 +1714,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2065106460</t>
+          <t>1391709606</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2065106460</t>
+          <t>https://m.place.naver.com/place/1391709606</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">

--- a/naver-place-crawler/results_health/김포_PT.xlsx
+++ b/naver-place-crawler/results_health/김포_PT.xlsx
@@ -427,7 +427,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="41" customWidth="1" min="7" max="7"/>
-    <col width="46" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
@@ -812,10 +812,10 @@
         <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R4" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -1029,39 +1029,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>빠짐 헬스&amp;재활PT 장기역점</t>
+          <t>인어스휘트니스 헬스 PT &amp; 필라테스 골프 김포점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jppark4@naver.com</t>
+          <t>inus-fitness09@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1316-2928</t>
+          <t>0507-1312-8337</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로97번길 32-32 1층</t>
+          <t>경기도 김포시 김포한강4로 113 신한프라자 10층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jppark4</t>
+          <t>https://inushnl.com/layout/fitness/home.php?go=main&amp;</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>70</v>
+        <v>1412</v>
       </c>
       <c r="Q7" t="n">
-        <v>409</v>
+        <v>800</v>
       </c>
       <c r="R7" t="n">
-        <v>479</v>
+        <v>2212</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1324417059</t>
+          <t>1901435715</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324417059</t>
+          <t>https://m.place.naver.com/place/1901435715</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1128,29 +1128,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G1 헬스&amp;PT 고촌점</t>
+          <t>빠짐 헬스&amp;재활PT 장기역점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>dmak77@naver.com</t>
+          <t>jppark4@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1358-1783</t>
+          <t>0507-1316-2928</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 김포시 고촌읍 수기로 115 센트럴타워 505호~507호</t>
+          <t>경기도 김포시 김포한강1로97번길 32-32 1층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dmak77?tab=1</t>
+          <t>https://blog.naver.com/jppark4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1185,13 +1185,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>298</v>
+        <v>70</v>
       </c>
       <c r="Q8" t="n">
-        <v>256</v>
+        <v>409</v>
       </c>
       <c r="R8" t="n">
-        <v>554</v>
+        <v>479</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1747463295</t>
+          <t>1324417059</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1747463295</t>
+          <t>https://m.place.naver.com/place/1324417059</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1315,39 +1315,39 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>모멘핏 재활PT 장기점</t>
+          <t>오픈도어복싱센터 ODBC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>dailyfitmemo@naver.com</t>
+          <t>odbc221008@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1338-0549</t>
+          <t>0507-1391-0736</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강3로237번길 10 1동 2층</t>
+          <t>경기 김포시 김포한강8로148번길 8-10 1층 102호</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/momentfit_janggi</t>
+          <t>https://opendoorboxing.imweb.me/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1357,18 +1357,22 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5i4rg</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1377,13 +1381,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>14</v>
+        <v>95</v>
       </c>
       <c r="Q10" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="R10" t="n">
-        <v>34</v>
+        <v>200</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1392,12 +1396,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>2096364009</t>
+          <t>1391709606</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2096364009</t>
+          <t>https://m.place.naver.com/place/1391709606</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1409,39 +1413,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>오픈도어복싱센터 ODBC</t>
+          <t>헨트 피트니스 헬스&amp;PT 풍무점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>odbc221008@naver.com</t>
+          <t>hentfitness@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1391-0736</t>
+          <t>0507-1310-2603</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강8로148번길 8-10 1층 102호</t>
+          <t>경기도 김포시 풍무로 112 4층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://opendoorboxing.imweb.me/</t>
+          <t>https://open.kakao.com/o/sO2iZ5Bh</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1451,19 +1455,15 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w5i4rg</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>O</t>
@@ -1475,13 +1475,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>95</v>
+        <v>203</v>
       </c>
       <c r="Q11" t="n">
-        <v>105</v>
+        <v>714</v>
       </c>
       <c r="R11" t="n">
-        <v>200</v>
+        <v>917</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1391709606</t>
+          <t>1735469913</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1391709606</t>
+          <t>https://m.place.naver.com/place/1735469913</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1512,25 +1512,29 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>휘트니스바로PT 고촌점</t>
+          <t>라운지휘트니스 헬스&amp;PT 구래점</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>fitnessbaro_2@naver.com</t>
+          <t>lounge_fitness2@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0507-1314-9498</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>경기도 김포시 고촌읍 태리로 293 3층</t>
+          <t>경기도 김포시 김포한강8로 304 3층 라운지 휘트니스 구래점</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://smartstore.naver.com/fitnessbaro</t>
+          <t>https://www.instagram.com/lounge__fitness2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1565,13 +1569,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>102</v>
+        <v>314</v>
       </c>
       <c r="Q12" t="n">
-        <v>48</v>
+        <v>166</v>
       </c>
       <c r="R12" t="n">
-        <v>150</v>
+        <v>480</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1580,12 +1584,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2065106460</t>
+          <t>1129008408</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2065106460</t>
+          <t>https://m.place.naver.com/place/1129008408</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">

--- a/naver-place-crawler/results_health/김포_PT.xlsx
+++ b/naver-place-crawler/results_health/김포_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -646,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 김포시 중봉1로 17 4층</t>
+          <t>경기 김포시 중봉1로 17 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w936str</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -718,10 +722,10 @@
         <v>338</v>
       </c>
       <c r="Q3" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="R3" t="n">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -740,41 +744,41 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>원알엠 PT&amp;헬스 풍무점</t>
+          <t>라임 피트니스 PT 김포장기점</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>sheep_coach@naver.com</t>
+          <t>lime___fitness@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1417-8271</t>
+          <t>0507-1381-7494</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 김포시 풍무로 105 가동 제6층 602호</t>
+          <t>경기 김포시 태장로 780 베네치아의 아침 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/sheep_coach</t>
+          <t>https://blog.naver.com/lime___fitness</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -794,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hh9p</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -809,13 +817,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>30</v>
+        <v>480</v>
       </c>
       <c r="Q4" t="n">
-        <v>100</v>
+        <v>494</v>
       </c>
       <c r="R4" t="n">
-        <v>130</v>
+        <v>974</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -824,17 +832,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2035326726</t>
+          <t>1802881557</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2035326726</t>
+          <t>https://m.place.naver.com/place/1802881557</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -846,29 +854,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>위너핏 마송점</t>
+          <t>원알엠 PT&amp;헬스 풍무점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>boos66@naver.com</t>
+          <t>sheep_coach@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1319-4816</t>
+          <t>0507-1417-8271</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 김포시 통진읍 마송1로84번길 53 7층</t>
+          <t>경기 김포시 풍무로 105 가동 제6층 602호</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/boos66</t>
+          <t>https://blog.naver.com/sheep_coach</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -888,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/ww7sj2s</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -903,13 +915,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>177</v>
+        <v>100</v>
       </c>
       <c r="R5" t="n">
-        <v>292</v>
+        <v>130</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,17 +930,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1043243355</t>
+          <t>2035326726</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1043243355</t>
+          <t>https://m.place.naver.com/place/2035326726</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -940,29 +952,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>루온짐PT 김포 장기점</t>
+          <t>위너핏 마송점</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>luongym@naver.com</t>
+          <t>boos66@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1355-1592</t>
+          <t>0507-1319-4816</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강2로 110 센타프라자 3층 301호</t>
+          <t>경기 김포시 통진읍 마송1로84번길 53 7층</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/luon.gym</t>
+          <t>https://blog.naver.com/boos66</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -977,15 +989,19 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5w0ua</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -997,13 +1013,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="Q6" t="n">
-        <v>437</v>
+        <v>178</v>
       </c>
       <c r="R6" t="n">
-        <v>554</v>
+        <v>293</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
@@ -1012,56 +1028,56 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1024850213</t>
+          <t>1043243355</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1024850213</t>
+          <t>https://m.place.naver.com/place/1043243355</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>인어스휘트니스 헬스 PT &amp; 필라테스 골프 김포점</t>
+          <t>루온짐PT 김포 장기점</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>inus-fitness09@naver.com</t>
+          <t>luongym@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1312-8337</t>
+          <t>0507-1355-1592</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강4로 113 신한프라자 10층</t>
+          <t>경기 김포시 김포한강2로 110 센타프라자 3층 301호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://inushnl.com/layout/fitness/home.php?go=main&amp;</t>
+          <t>https://www.instagram.com/luon.gym</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1076,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wvx1m86</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1091,13 +1111,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>1412</v>
+        <v>118</v>
       </c>
       <c r="Q7" t="n">
-        <v>800</v>
+        <v>437</v>
       </c>
       <c r="R7" t="n">
-        <v>2212</v>
+        <v>555</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,56 +1126,56 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1901435715</t>
+          <t>1024850213</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1901435715</t>
+          <t>https://m.place.naver.com/place/1024850213</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>빠짐 헬스&amp;재활PT 장기역점</t>
+          <t>인어스휘트니스 헬스 PT &amp; 필라테스 골프 김포점</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jppark4@naver.com</t>
+          <t>inus-fitness09@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0507-1316-2928</t>
+          <t>0507-1312-8337</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로97번길 32-32 1층</t>
+          <t>경기 김포시 김포한강4로 113 신한프라자 10층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/jppark4</t>
+          <t>https://inushnl.com/layout/fitness/home.php?go=main&amp;</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1165,15 +1185,19 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45d2f</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1185,13 +1209,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>70</v>
+        <v>1412</v>
       </c>
       <c r="Q8" t="n">
-        <v>409</v>
+        <v>801</v>
       </c>
       <c r="R8" t="n">
-        <v>479</v>
+        <v>2213</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,51 +1224,51 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1324417059</t>
+          <t>1901435715</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1324417059</t>
+          <t>https://m.place.naver.com/place/1901435715</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>플랜휘트니스 사우역점</t>
+          <t>빠짐 헬스&amp;재활PT 장기역점</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>planfitness89@naver.com</t>
+          <t>jppark4@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1395-4251</t>
+          <t>0507-1316-2928</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 김포시 사우중로 87 5층</t>
+          <t>경기 김포시 김포한강1로97번길 32-32 1층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/planfitness89</t>
+          <t>https://blog.naver.com/jppark4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1269,7 +1293,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/wavreq8</t>
+          <t>https://talk.naver.com/ct/wcefw2</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1283,13 +1307,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>331</v>
+        <v>70</v>
       </c>
       <c r="Q9" t="n">
-        <v>194</v>
+        <v>409</v>
       </c>
       <c r="R9" t="n">
-        <v>525</v>
+        <v>479</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1298,51 +1322,51 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1427280856</t>
+          <t>1324417059</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1427280856</t>
+          <t>https://m.place.naver.com/place/1324417059</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>복싱,권투장</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>오픈도어복싱센터 ODBC</t>
+          <t>엑스짐 헬스 PT 김포장기동점</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>odbc221008@naver.com</t>
+          <t>cltnzz6736@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0507-1391-0736</t>
+          <t>0507-1327-6736</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>경기 김포시 김포한강8로148번길 8-10 1층 102호</t>
+          <t>경기 김포시 김포한강4로 129 하나프라자 7층</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://opendoorboxing.imweb.me/</t>
+          <t>https://zhenghwun91.wixsite.com/xgym</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1352,7 +1376,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1367,7 +1391,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://talk.naver.com/ct/w5i4rg</t>
+          <t>https://talk.naver.com/ct/w497xw</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1381,13 +1405,13 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="Q10" t="n">
-        <v>105</v>
+        <v>186</v>
       </c>
       <c r="R10" t="n">
-        <v>200</v>
+        <v>410</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1396,17 +1420,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1391709606</t>
+          <t>1567234519</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1391709606</t>
+          <t>https://m.place.naver.com/place/1567234519</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -1418,29 +1442,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>헨트 피트니스 헬스&amp;PT 풍무점</t>
+          <t>플랜휘트니스 사우역점</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hentfitness@naver.com</t>
+          <t>planfitness89@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1310-2603</t>
+          <t>0507-1395-4251</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 김포시 풍무로 112 4층</t>
+          <t>경기 김포시 사우중로 87 5층</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://open.kakao.com/o/sO2iZ5Bh</t>
+          <t>https://blog.naver.com/planfitness89</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1455,18 +1479,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wavreq8</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1475,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>203</v>
+        <v>331</v>
       </c>
       <c r="Q11" t="n">
-        <v>714</v>
+        <v>194</v>
       </c>
       <c r="R11" t="n">
-        <v>917</v>
+        <v>525</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,111 +1518,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1735469913</t>
+          <t>1427280856</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1735469913</t>
+          <t>https://m.place.naver.com/place/1427280856</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>라운지휘트니스 헬스&amp;PT 구래점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>lounge_fitness2@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1314-9498</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기도 김포시 김포한강8로 304 3층 라운지 휘트니스 구래점</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/lounge__fitness2</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>314</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>166</v>
-      </c>
-      <c r="R12" t="n">
-        <v>480</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1129008408</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1129008408</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/김포_PT.xlsx
+++ b/naver-place-crawler/results_health/김포_PT.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V13"/>
+  <dimension ref="A1:V11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -675,7 +675,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>경기도 김포시 중봉1로 17 4층</t>
+          <t>경기 김포시 중봉1로 17 4층</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -700,10 +700,14 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w936str</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>X</t>
@@ -718,10 +722,10 @@
         <v>338</v>
       </c>
       <c r="Q3" t="n">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="R3" t="n">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -769,7 +773,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>경기도 김포시 태장로 780 베네치아의 아침 3층</t>
+          <t>경기 김포시 태장로 780 베네치아의 아침 3층</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -794,10 +798,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w4hh9p</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>X</t>
@@ -863,7 +871,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강1로97번길 32-32 1층</t>
+          <t>경기 김포시 김포한강1로97번길 32-32 1층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -888,10 +896,14 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wcefw2</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>X</t>
@@ -957,7 +969,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>경기도 김포시 풍무로 105 가동 제6층 602호</t>
+          <t>경기 김포시 풍무로 105 가동 제6층 602호</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -982,10 +994,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/ww7sj2s</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>X</t>
@@ -1051,7 +1067,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강2로 110 센타프라자 3층 301호</t>
+          <t>경기 김포시 김포한강2로 110 센타프라자 3층 301호</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1076,10 +1092,14 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/wvx1m86</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>X</t>
@@ -1243,7 +1263,7 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강4로 113 신한프라자 10층</t>
+          <t>경기 김포시 김포한강4로 113 신한프라자 10층</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1268,10 +1288,14 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w45d2f</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>X</t>
@@ -1413,39 +1437,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>복싱,권투장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>모멘핏 재활PT 장기점</t>
+          <t>오픈도어복싱센터 ODBC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>dailyfitmemo@naver.com</t>
+          <t>odbc221008@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0507-1338-0549</t>
+          <t>0507-1391-0736</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>경기도 김포시 김포한강3로237번길 10 1동 2층</t>
+          <t>경기 김포시 김포한강8로148번길 8-10 1층 102호</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/momentfit_janggi</t>
+          <t>https://opendoorboxing.imweb.me/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1455,18 +1479,22 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>https://talk.naver.com/ct/w5i4rg</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1475,13 +1503,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>15</v>
+        <v>96</v>
       </c>
       <c r="Q11" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="R11" t="n">
-        <v>35</v>
+        <v>201</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1490,203 +1518,15 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2096364009</t>
+          <t>1391709606</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2096364009</t>
+          <t>https://m.place.naver.com/place/1391709606</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>라운지휘트니스 헬스&amp;PT 구래점</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>lounge_fitness2@naver.com</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0507-1314-9498</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>경기 김포시 김포한강8로 304 3층 라운지 휘트니스 구래점</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/lounge__fitness2</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/wc359u9</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P12" t="n">
-        <v>314</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>166</v>
-      </c>
-      <c r="R12" t="n">
-        <v>480</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>1129008408</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/1129008408</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>헬스장</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>휘트니스바로PT 고촌점</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>fitnessbaro_2@naver.com</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>경기도 김포시 고촌읍 태리로 293 3층</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>https://smartstore.naver.com/fitnessbaro</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="P13" t="n">
-        <v>103</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>48</v>
-      </c>
-      <c r="R13" t="n">
-        <v>151</v>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>2065106460</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>https://m.place.naver.com/place/2065106460</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
